--- a/4_Regulatory_Compliance/MT-DSGVO-RoPA-001_v1.0_records-of-processing-activities.xlsx
+++ b/4_Regulatory_Compliance/MT-DSGVO-RoPA-001_v1.0_records-of-processing-activities.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="96">
   <si>
     <t>MunichTech GmbH</t>
   </si>
@@ -48,7 +48,7 @@
     <t>Effective Date</t>
   </si>
   <si>
-    <t>[Date]</t>
+    <t/>
   </si>
   <si>
     <t>Austin Bond, Junior GRC Consultant</t>
@@ -97,7 +97,7 @@
     <t>Approved By</t>
   </si>
   <si>
-    <t>[Senior GRC Partner Name], CISM, ISO LA</t>
+    <t>Dr. Andreas Kellermann, CISM, ISO LA</t>
   </si>
   <si>
     <t>Head of Sales</t>
@@ -211,7 +211,7 @@
     <t>Salesforce Shield Encryption, MFA enforced for all Sales staff, DLP blocking mass exports.</t>
   </si>
   <si>
-    <t>Managed via formal Works Council agreement (Betriebsvereinbarung). Logs are WORM protected.</t>
+    <t>Managed via formal Works Council agreement (Betriebsvereinbarung MT-WorksCouncil-CrowdStrike-v1.2). Logs are WORM protected.</t>
   </si>
   <si>
     <t>Data Protection Officer (DPO) / Legal Counsel</t>
@@ -307,7 +307,7 @@
     <t>Joint Controllership:</t>
   </si>
   <si>
-    <t>[Fictional Street Address], 80331 Munich, Germany</t>
+    <t/>
   </si>
   <si>
     <t>privacy@munichtech.de</t>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>Provided by the Data Controller (Enterprise Client)</t>
+  </si>
+  <si>
+    <t>5 November 2025</t>
+  </si>
+  <si>
+    <t>Balanstraße 73, 81541 Munich, Germany</t>
   </si>
 </sst>
 </file>
@@ -960,7 +966,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -1026,7 +1032,7 @@
         <v>81</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="2:13">
